--- a/Altium/elecrow fabrication/DTCP elecrow BOM.xlsx
+++ b/Altium/elecrow fabrication/DTCP elecrow BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\Desktop\dtcp design 1\dtcp\Altium\elecrow fabrication\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdado\Desktop\dtcp\dtcp\Altium\elecrow fabrication\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CA0BA65-73EC-4C6F-B33E-12CF39BED0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1294F2-3F17-4A5E-AF33-5F2F259FDFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="112">
   <si>
     <t>*Reference</t>
   </si>
@@ -262,12 +262,6 @@
     <t>150120SS75000</t>
   </si>
   <si>
-    <t>HSMG-C150</t>
-  </si>
-  <si>
-    <t>613010143121</t>
-  </si>
-  <si>
     <t>SMA-J-P-H-ST-EM1</t>
   </si>
   <si>
@@ -286,9 +280,6 @@
     <t>MABAES0060</t>
   </si>
   <si>
-    <t>TSW-102-08-G-S-RA</t>
-  </si>
-  <si>
     <t>CRGCQ0603J10K</t>
   </si>
   <si>
@@ -338,9 +329,6 @@
   </si>
   <si>
     <t>CRGP0805F10K</t>
-  </si>
-  <si>
-    <t>452406020024</t>
   </si>
   <si>
     <t>MSPM0C1104SDGS20R</t>
@@ -879,16 +867,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="110.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="1" max="1" width="110.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="27.5546875" customWidth="1"/>
     <col min="4" max="4" width="12" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="29.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="13.8">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -908,7 +896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" ht="18.95" customHeight="1">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>8</v>
       </c>
@@ -972,7 +960,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="15.95" customHeight="1">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="15.9" customHeight="1">
       <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
@@ -988,7 +976,7 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="15.75">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="15.6">
       <c r="A7" s="11" t="s">
         <v>13</v>
       </c>
@@ -1004,7 +992,7 @@
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" ht="15.75">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="15.6">
       <c r="A8" s="11" t="s">
         <v>14</v>
       </c>
@@ -1020,7 +1008,7 @@
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="15.75">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="15.6">
       <c r="A9" s="11" t="s">
         <v>15</v>
       </c>
@@ -1036,7 +1024,7 @@
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="15.75">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="15.6">
       <c r="A10" s="11" t="s">
         <v>16</v>
       </c>
@@ -1052,7 +1040,7 @@
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" ht="15.75">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="15.6">
       <c r="A11" s="11" t="s">
         <v>17</v>
       </c>
@@ -1068,7 +1056,7 @@
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75">
+    <row r="12" spans="1:6" ht="15.6">
       <c r="A12" s="11" t="s">
         <v>18</v>
       </c>
@@ -1084,7 +1072,7 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75">
+    <row r="13" spans="1:6" ht="15.6">
       <c r="A13" s="11" t="s">
         <v>19</v>
       </c>
@@ -1100,7 +1088,7 @@
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75">
+    <row r="14" spans="1:6" ht="15.6">
       <c r="A14" s="11" t="s">
         <v>20</v>
       </c>
@@ -1116,7 +1104,7 @@
       <c r="E14" s="15"/>
       <c r="F14" s="15"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75">
+    <row r="15" spans="1:6" ht="15.6">
       <c r="A15" s="11" t="s">
         <v>21</v>
       </c>
@@ -1132,7 +1120,7 @@
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75">
+    <row r="16" spans="1:6" ht="15.6">
       <c r="A16" s="11" t="s">
         <v>22</v>
       </c>
@@ -1148,7 +1136,7 @@
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75">
+    <row r="17" spans="1:6" ht="15.6">
       <c r="A17" s="11" t="s">
         <v>23</v>
       </c>
@@ -1164,7 +1152,7 @@
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75">
+    <row r="18" spans="1:6" ht="15.6">
       <c r="A18" s="11" t="s">
         <v>24</v>
       </c>
@@ -1180,12 +1168,12 @@
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75">
+    <row r="19" spans="1:6" ht="15.6">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C19" s="12">
         <v>1</v>
@@ -1196,12 +1184,12 @@
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75">
+    <row r="20" spans="1:6" ht="15.6">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C20" s="12">
         <v>3</v>
@@ -1212,12 +1200,12 @@
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75">
+    <row r="21" spans="1:6" ht="15.6">
       <c r="A21" s="11" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C21" s="12">
         <v>5</v>
@@ -1228,12 +1216,12 @@
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75">
+    <row r="22" spans="1:6" ht="15.6">
       <c r="A22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C22" s="12">
         <v>2</v>
@@ -1244,12 +1232,12 @@
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75">
+    <row r="23" spans="1:6" ht="15.6">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" s="12">
         <v>1</v>
@@ -1260,12 +1248,12 @@
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75">
+    <row r="24" spans="1:6" ht="15.6">
       <c r="A24" s="11" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C24" s="12">
         <v>1</v>
@@ -1276,12 +1264,12 @@
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75">
+    <row r="25" spans="1:6" ht="15.6">
       <c r="A25" s="11" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C25" s="12">
         <v>1</v>
@@ -1292,12 +1280,12 @@
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75">
+    <row r="26" spans="1:6" ht="15.6">
       <c r="A26" s="11" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C26" s="12">
         <v>3</v>
@@ -1308,12 +1296,12 @@
       <c r="E26" s="15"/>
       <c r="F26" s="15"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75">
+    <row r="27" spans="1:6" ht="15.6">
       <c r="A27" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C27" s="12">
         <v>1</v>
@@ -1324,12 +1312,12 @@
       <c r="E27" s="15"/>
       <c r="F27" s="15"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75">
+    <row r="28" spans="1:6" ht="15.6">
       <c r="A28" s="11" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C28" s="12">
         <v>2</v>
@@ -1340,12 +1328,12 @@
       <c r="E28" s="15"/>
       <c r="F28" s="15"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75">
+    <row r="29" spans="1:6" ht="15.6">
       <c r="A29" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C29" s="12">
         <v>11</v>
@@ -1356,12 +1344,12 @@
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75">
+    <row r="30" spans="1:6" ht="15.6">
       <c r="A30" s="11" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C30" s="12">
         <v>1</v>
@@ -1372,12 +1360,12 @@
       <c r="E30" s="15"/>
       <c r="F30" s="15"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75">
+    <row r="31" spans="1:6" ht="15.6">
       <c r="A31" s="11" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C31" s="12">
         <v>1</v>
@@ -1388,15 +1376,15 @@
       <c r="E31" s="15"/>
       <c r="F31" s="15"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75">
+    <row r="32" spans="1:6" ht="15.6">
       <c r="A32" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C32" s="12">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D32" s="16" t="s">
         <v>7</v>
@@ -1404,12 +1392,12 @@
       <c r="E32" s="15"/>
       <c r="F32" s="15"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75">
+    <row r="33" spans="1:6" ht="15.6">
       <c r="A33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C33" s="12">
         <v>2</v>
@@ -1420,12 +1408,12 @@
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75">
+    <row r="34" spans="1:6" ht="15.6">
       <c r="A34" s="11" t="s">
         <v>40</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C34" s="12">
         <v>1</v>
@@ -1436,12 +1424,12 @@
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75">
+    <row r="35" spans="1:6" ht="15.6">
       <c r="A35" s="11" t="s">
         <v>41</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C35" s="12">
         <v>2</v>
@@ -1452,12 +1440,12 @@
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75">
+    <row r="36" spans="1:6" ht="15.6">
       <c r="A36" s="11" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C36" s="12">
         <v>5</v>
@@ -1468,12 +1456,12 @@
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75">
+    <row r="37" spans="1:6" ht="15.6">
       <c r="A37" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C37" s="12">
         <v>2</v>
@@ -1484,12 +1472,12 @@
       <c r="E37" s="15"/>
       <c r="F37" s="15"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75">
+    <row r="38" spans="1:6" ht="15.6">
       <c r="A38" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C38" s="12">
         <v>2</v>
@@ -1500,12 +1488,12 @@
       <c r="E38" s="15"/>
       <c r="F38" s="15"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75">
+    <row r="39" spans="1:6" ht="15.6">
       <c r="A39" s="11" t="s">
         <v>45</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C39" s="12">
         <v>2</v>
@@ -1516,12 +1504,12 @@
       <c r="E39" s="15"/>
       <c r="F39" s="15"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75">
+    <row r="40" spans="1:6" ht="15.6">
       <c r="A40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C40" s="12">
         <v>1</v>
@@ -1532,12 +1520,12 @@
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75">
+    <row r="41" spans="1:6" ht="15.6">
       <c r="A41" s="11" t="s">
         <v>47</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C41" s="12">
         <v>1</v>
@@ -1548,12 +1536,12 @@
       <c r="E41" s="15"/>
       <c r="F41" s="15"/>
     </row>
-    <row r="42" spans="1:6" ht="15.75">
+    <row r="42" spans="1:6" ht="15.6">
       <c r="A42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C42" s="12">
         <v>1</v>
@@ -1564,12 +1552,12 @@
       <c r="E42" s="15"/>
       <c r="F42" s="15"/>
     </row>
-    <row r="43" spans="1:6" ht="15.75">
+    <row r="43" spans="1:6" ht="15.6">
       <c r="A43" s="11" t="s">
         <v>49</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C43" s="12">
         <v>1</v>
@@ -1580,12 +1568,12 @@
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75">
+    <row r="44" spans="1:6" ht="15.6">
       <c r="A44" s="11" t="s">
         <v>50</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C44" s="12">
         <v>1</v>
@@ -1596,12 +1584,12 @@
       <c r="E44" s="15"/>
       <c r="F44" s="15"/>
     </row>
-    <row r="45" spans="1:6" ht="15.75">
+    <row r="45" spans="1:6" ht="15.6">
       <c r="A45" s="11" t="s">
         <v>51</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C45" s="12">
         <v>2</v>
@@ -1612,12 +1600,12 @@
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
     </row>
-    <row r="46" spans="1:6" ht="15.75">
+    <row r="46" spans="1:6" ht="15.6">
       <c r="A46" s="11" t="s">
         <v>52</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C46" s="12">
         <v>1</v>
@@ -1628,28 +1616,28 @@
       <c r="E46" s="15"/>
       <c r="F46" s="15"/>
     </row>
-    <row r="47" spans="1:6" ht="15.75">
+    <row r="47" spans="1:6" ht="15.6">
       <c r="A47" s="11" t="s">
         <v>53</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C47" s="12">
         <v>1</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="15"/>
     </row>
-    <row r="48" spans="1:6" ht="15.75">
+    <row r="48" spans="1:6" ht="15.6">
       <c r="A48" s="11" t="s">
         <v>54</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C48" s="12">
         <v>1</v>
@@ -1660,12 +1648,12 @@
       <c r="E48" s="15"/>
       <c r="F48" s="15"/>
     </row>
-    <row r="49" spans="1:6" ht="15.75">
+    <row r="49" spans="1:6" ht="15.6">
       <c r="A49" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C49" s="12">
         <v>2</v>
@@ -1676,12 +1664,12 @@
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
     </row>
-    <row r="50" spans="1:6" ht="15.75">
+    <row r="50" spans="1:6" ht="15.6">
       <c r="A50" s="11" t="s">
         <v>56</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C50" s="12">
         <v>2</v>
@@ -1692,12 +1680,12 @@
       <c r="E50" s="15"/>
       <c r="F50" s="15"/>
     </row>
-    <row r="51" spans="1:6" ht="15.75">
+    <row r="51" spans="1:6" ht="15.6">
       <c r="A51" s="11" t="s">
         <v>57</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C51" s="12">
         <v>1</v>
@@ -1708,12 +1696,12 @@
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
     </row>
-    <row r="52" spans="1:6" ht="15.75">
+    <row r="52" spans="1:6" ht="15.6">
       <c r="A52" s="11" t="s">
         <v>58</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C52" s="12">
         <v>1</v>
@@ -1724,12 +1712,12 @@
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
     </row>
-    <row r="53" spans="1:6" ht="15.75">
+    <row r="53" spans="1:6" ht="15.6">
       <c r="A53" s="11" t="s">
         <v>59</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C53" s="12">
         <v>1</v>
@@ -1740,12 +1728,12 @@
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
     </row>
-    <row r="54" spans="1:6" ht="15.75">
+    <row r="54" spans="1:6" ht="15.6">
       <c r="A54" s="11" t="s">
         <v>60</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C54" s="12">
         <v>1</v>
@@ -1756,12 +1744,12 @@
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
     </row>
-    <row r="55" spans="1:6" ht="15.75">
+    <row r="55" spans="1:6" ht="15.6">
       <c r="A55" s="11" t="s">
         <v>61</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C55" s="12">
         <v>1</v>
@@ -1772,12 +1760,12 @@
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
     </row>
-    <row r="56" spans="1:6" ht="15.75">
+    <row r="56" spans="1:6" ht="15.6">
       <c r="A56" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C56" s="12">
         <v>1</v>
